--- a/src/src/main/webapp/portal/zkb/salesPerson/excel/APM_ZKB_SalePerson_Imp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/salesPerson/excel/APM_ZKB_SalePerson_Imp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\salesPerson\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A01E276-2337-4C2B-954C-BC946D7EED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0E644D-C41F-4984-9466-E6564A25B207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="358" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -31,9 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>租户id</t>
+  </si>
+  <si>
+    <t>租户名称</t>
   </si>
 </sst>
 </file>
@@ -385,17 +388,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644DDB6A-FFA4-49B3-B3EB-E6F6582E54C5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" customWidth="1"/>
     <col min="11" max="11" width="20.28515625" customWidth="1"/>
     <col min="12" max="12" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
